--- a/回後買上漲圖表(基礎版)_20260603/回後買上漲基礎版_20260603.xlsx
+++ b/回後買上漲圖表(基礎版)_20260603/回後買上漲基礎版_20260603.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="掃描標的" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +28,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F8"/>
+        <bgColor rgb="00F2F5F8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,19 +73,54 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,10 +487,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
@@ -451,162 +524,4821 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>今昨量倍數</t>
+          <t>今日成交量(張)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>今日成交量(張)</t>
+          <t>五日均量(張)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>昨日成交量(張)</t>
+          <t>量能放大倍數</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>均線狀態</t>
+          <t>月線位置(20MA)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>回測支撐</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
           <t>雅虎股市連結</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>9933.TW</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>20295</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>7247</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1616.TW</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>億泰</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3586</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>1313</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2031.TW</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>4229</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1618.TW</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>6144</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>2425</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1217.TW</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>愛之味</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2975</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1187</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>4976.TW</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>佳凌</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3444</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>1451</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>8076.TWO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>伍豐</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>6570</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2693</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>1612.TW</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>宏泰</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>2418</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1608.TW</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>華榮</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>32957</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>14128</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>5381.TWO</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>光譜</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>4110</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1809</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2371.TW</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>大同</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>67652</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>28869</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>5009.TWO</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>榮剛</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>9852</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>4577</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>9934.TW</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>成霖</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>3289.TWO</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>宜特</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>5793</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>2602</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6907.TWO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>雅特力-KY</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>3834</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1793</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>1513.TW</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>45918</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>21375</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>159.68</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>1447.TW</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>力鵬</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>8853</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>4302</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>1907.TW</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>永豐餘</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>4037</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2030.TW</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>彰源</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>3463</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>1529.TW</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>樂事綠能</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>2870</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1421</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>1444.TW</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>力麗</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>10873</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>5430</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2022.TW</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>聚亨</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>2831</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1524</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1514.TW</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>22363</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>11970</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>3376.TW</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>新日興</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>226.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>14181</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>7411</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>208.05</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1519.TW</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>935</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>9078</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>4859</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>856.35</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>3483.TWO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>力致</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
         <v>110.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D27" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="E27" s="9" t="n">
         <v>4239</v>
       </c>
-      <c r="G2" t="n">
-        <v>2088</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://tw.stock.yahoo.com/quote/3483</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>6126.TWO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6126</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>42.65</v>
-      </c>
-      <c r="D3" t="n">
-        <v>39.15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>15696</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5991</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>https://tw.stock.yahoo.com/quote/6126</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2317.TW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>309</v>
-      </c>
-      <c r="D4" t="n">
-        <v>302</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="F27" s="9" t="n">
+        <v>2196</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>93.73</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2342.TW</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>茂矽</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>15846</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>9054</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2014.TW</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>中鴻</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>18193</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>10324</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2032.TW</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>新鋼</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>2256</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1335</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>6869.TW</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>雲豹能源</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1777</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>1032</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>6163.TWO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>華電網</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>7756</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>4637</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>9939.TW</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>宏全</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>2340</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1399</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>1709.TW</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>和益</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>2368</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1415</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>5530.TWO</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>龍巖</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>3493</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>2001</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>3093.TWO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>港建*</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1951</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1163</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>1304.TW</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>台聚</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>18561</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>11898</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>9103.TW</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>美德醫療-DR</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1939</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>6226.TW</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>光鼎</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>4992</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>3049</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>3362.TWO</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>3561</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>2199</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>6269.TW</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>台郡</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>24820</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>15406</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2851.TW</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>中再保</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>3626</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>2457.TW</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>飛宏</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>8254</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>5007</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>3041.TW</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>揚智</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>2733</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1734</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>9958.TW</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>世紀鋼</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>107</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>4257</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>2675</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>4714.TWO</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>永捷</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1137</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>2515.TW</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>中工</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>13827</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>9162</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2406.TW</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>國碩</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>28888</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>19090</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>8422.TW</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>可寧衛*</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>19416</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>12757</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>6873.TW</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>泓德能源</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>1553</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1066</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>5228.TWO</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>鈺鎧</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>1808</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>3374.TWO</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>33215</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>22881</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>249.8</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>3015.TW</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>全漢</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>3198</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>2177</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2034.TW</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>3253</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>2119</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>4763.TW</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>材料*-KY</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>12731</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>8490</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2504.TW</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>國產</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>4771</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>3449</v>
+      </c>
+      <c r="G56" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="F4" t="n">
-        <v>149311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>110375</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>https://tw.stock.yahoo.com/quote/2317</t>
+      <c r="H56" s="3" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2392.TW</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>正崴</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>7198</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>5052</v>
+      </c>
+      <c r="G57" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>6530.TWO</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>創威</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>6781.TW</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>AES-KY</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>2256</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>1568</v>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>1194.75</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>6129.TWO</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>普誠</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>2583</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1898</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>6133.TW</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>金橋</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>1401</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>3211.TWO</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>順達</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>464</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>441.5</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>16622</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>11683</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>1609.TW</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>大亞</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>31405</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>22561</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>35.97</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>3717.TW</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>聯嘉投控</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>3672</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>2564</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>8182.TWO</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>加高</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>8575</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>6205</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2002.TW</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>111525</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>82464</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>2484.TW</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>希華</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>35433</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>26096</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2023.TW</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>燁輝</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>3574</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>2488</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>4908.TWO</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>前鼎</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>251</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>249.5</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>5126</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>3878</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>244.75</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>5536.TWO</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>聖暉*</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>2195</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>1747</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>968.4</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>4532.TW</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>瑞智</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>1598</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2368.TW</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>7459</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>1344</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>3689.TWO</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>7613</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>5608.TW</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>四維航</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>3098</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>2332</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>3615.TWO</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>12475</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>9339</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2211.TW</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>長榮鋼</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>1610</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1246</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>94.22</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>4934.TW</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>太極</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>2152</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>1656</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>8104.TW</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>錸寶</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>8435</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>2442.TW</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>新美齊</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>3483</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>2697</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>1532.TW</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>勤美</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>1417</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>1147</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>1504.TW</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>95854</v>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>77534</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2486.TW</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>一詮</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>11993</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>9942</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>268.36</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>3017.TW</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>2855</v>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>2835</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>6892</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>5734</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>2564.75</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>6244.TWO</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>茂迪</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>15355</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>12326</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>3265.TWO</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>190</v>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>3104</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>2595</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>6179.TWO</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>亞通</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>1953</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>1604</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>2493.TW</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>揚博</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>5998</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>5411</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2351.TW</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>順德</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>8936</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>8302</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>192.85</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>6257.TW</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>15032</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>13232</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>219.18</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>5469.TW</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>瀚宇博</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>5089</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>4528</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>2010.TW</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>春源</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>1961</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>4534.TWO</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>慶騰</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>2466</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>2579</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>5210.TWO</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>寶碩</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>1257</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2301.TW</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>48437</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>48113</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>220.42</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>1560.TW</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="n">
+        <v>727</v>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>1617</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>1692</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>669.75</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2340.TW</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>台亞</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>7707</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>8102</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>8936.TWO</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>國統</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>5504</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>5571</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>6693.TWO</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>廣閎科</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>1015</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>1043</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>2345.TW</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>2585</v>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>2520</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>4084</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>4141</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>2501</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2538.TW</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>基泰</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>1309</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>1370</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>3576.TW</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>聯合再生</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>24358</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>23345</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>3481.TW</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>936130</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>942212</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>4541.TWO</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>晟田</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>1665</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>6442.TW</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>2065</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>2927</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>2828</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>1911.75</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>8215.TW</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>明基材</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>8725</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>8907</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>3711.TW</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>618</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>608</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>28514</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>30272</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>561.85</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>1476.TW</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>儒鴻</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>340.58</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>3363.TWO</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>上詮</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>884</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>864</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>2624</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>2942</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>835.35</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>4931.TWO</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>新盛力</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>254</v>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>10838</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>11703</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>1515.TW</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>力山</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>1104</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>1187</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>6227.TWO</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>茂綸</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>2218</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>2862</v>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>119.48</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>3490.TWO</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>單井</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>1781</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>2114</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>2501.TW</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>國建</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>3379</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>4126</v>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>79033</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>110641</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>0052.TW</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>富邦科技</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>23282</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>34914</v>
+      </c>
+      <c r="G115" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H115" s="8" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>3003.TW</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>健和興</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>835</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>1177</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>4739.TW</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>康普</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>5025</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>6757</v>
+      </c>
+      <c r="G117" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H117" s="8" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>3031.TW</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>佰鴻</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>3204</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>4147.TWO</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>中裕</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>2314</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>3164</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>4916.TW</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>事欣科</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>3663</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>5267</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>88.87</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>6182.TWO</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>合晶</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>8974</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>12897</v>
+      </c>
+      <c r="G121" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>3264.TWO</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>15736</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>21095</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>226.68</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>2207.TW</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>和泰車</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="n">
+        <v>485</v>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>975</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>470.58</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>3528.TW</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>安馳</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>1334</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>2095</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>2481.TW</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>33788</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>52476</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>132.28</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>3708.TW</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>923</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>1477</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>7769.TW</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="n">
+        <v>7525</v>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>7480</v>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>713</v>
+      </c>
+      <c r="F127" s="9" t="n">
+        <v>1189</v>
+      </c>
+      <c r="G127" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H127" s="8" t="n">
+        <v>7197</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>4923.TWO</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>力士</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>1283</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>2247</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>8064.TWO</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>東捷</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>9040</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>15425</v>
+      </c>
+      <c r="G129" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H129" s="8" t="n">
+        <v>132.15</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2610.TW</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>華航</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>55573</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>111081</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>6207.TWO</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>雷科</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>7428</v>
+      </c>
+      <c r="F131" s="9" t="n">
+        <v>16124</v>
+      </c>
+      <c r="G131" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>6415.TW</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>599</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>598</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>3761</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>6950</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>538.55</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>6223.TWO</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="n">
+        <v>5900</v>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>5695</v>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G133" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H133" s="8" t="n">
+        <v>5772.75</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>6456.TW</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>GIS-KY</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>7639</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>24682</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId133"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>